--- a/logs/logv7_divergências_bases_qdd_.xlsx
+++ b/logs/logv7_divergências_bases_qdd_.xlsx
@@ -9727,7 +9727,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA - SEAPA</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="H106" t="n">

--- a/logs/logv7_divergências_bases_qdd_.xlsx
+++ b/logs/logv7_divergências_bases_qdd_.xlsx
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>130320</v>
+        <v>130820</v>
       </c>
       <c r="AA67" t="n">
-        <v>-130320</v>
+        <v>-130820</v>
       </c>
     </row>
     <row r="68">
@@ -6797,7 +6797,7 @@
         <v>23</v>
       </c>
       <c r="P73" t="n">
-        <v>334</v>
+        <v>691</v>
       </c>
       <c r="Q73" t="n">
         <v>132</v>
@@ -6806,10 +6806,10 @@
         <v>1</v>
       </c>
       <c r="S73" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T73" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="U73" t="n">
         <v>1</v>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>CRÉDITO A EMPRESAS DA BACIA DO RIO DOCE</t>
+          <t>FOMENTO  AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -6828,10 +6828,10 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>250</v>
+        <v>185230</v>
       </c>
       <c r="AA73" t="n">
-        <v>-250</v>
+        <v>-185230</v>
       </c>
     </row>
     <row r="74">
@@ -6858,16 +6858,16 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K74" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L74" t="n">
         <v>80</v>
@@ -6879,7 +6879,7 @@
         <v>23</v>
       </c>
       <c r="P74" t="n">
-        <v>334</v>
+        <v>691</v>
       </c>
       <c r="Q74" t="n">
         <v>132</v>
@@ -6888,10 +6888,10 @@
         <v>1</v>
       </c>
       <c r="S74" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="T74" t="n">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="U74" t="n">
         <v>1</v>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>GARANTIA DE CRÉDITOS A EMPRESAS DA BACIA DO RIO DOCE</t>
+          <t>FOMENTO  AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>250</v>
+        <v>3000000</v>
       </c>
       <c r="AA74" t="n">
-        <v>-250</v>
+        <v>-3000000</v>
       </c>
     </row>
     <row r="75">
@@ -6940,16 +6940,16 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J75" t="n">
         <v>90</v>
       </c>
       <c r="K75" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L75" t="n">
         <v>80</v>
@@ -6961,7 +6961,7 @@
         <v>23</v>
       </c>
       <c r="P75" t="n">
-        <v>691</v>
+        <v>334</v>
       </c>
       <c r="Q75" t="n">
         <v>132</v>
@@ -6970,10 +6970,10 @@
         <v>1</v>
       </c>
       <c r="S75" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="T75" t="n">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="U75" t="n">
         <v>1</v>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>FOMENTO  AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
+          <t>GARANTIA DE CRÉDITOS A EMPRESAS DA BACIA DO RIO DOCE</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>185230</v>
+        <v>33921382</v>
       </c>
       <c r="AA75" t="n">
-        <v>-185230</v>
+        <v>-33921382</v>
       </c>
     </row>
     <row r="76">
@@ -7025,13 +7025,13 @@
         <v>4</v>
       </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K76" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="L76" t="n">
         <v>80</v>
@@ -7043,7 +7043,7 @@
         <v>23</v>
       </c>
       <c r="P76" t="n">
-        <v>691</v>
+        <v>334</v>
       </c>
       <c r="Q76" t="n">
         <v>132</v>
@@ -7052,10 +7052,10 @@
         <v>1</v>
       </c>
       <c r="S76" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T76" t="n">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="U76" t="n">
         <v>1</v>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>FOMENTO  AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
+          <t>CRÉDITO A EMPRESAS DA BACIA DO RIO DOCE</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>11720382</v>
+        <v>45000000</v>
       </c>
       <c r="AA76" t="n">
-        <v>-11720382</v>
+        <v>-45000000</v>
       </c>
     </row>
     <row r="77">
@@ -7827,18 +7827,18 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IGAM</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D86" t="n">
         <v>3</v>
       </c>
       <c r="F86" t="n">
-        <v>2241</v>
+        <v>2101</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS - IGAM</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -7851,7 +7851,7 @@
         <v>50</v>
       </c>
       <c r="K86" t="n">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="L86" t="n">
         <v>80</v>
@@ -7863,19 +7863,19 @@
         <v>18</v>
       </c>
       <c r="P86" t="n">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="Q86" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="R86" t="n">
         <v>4</v>
       </c>
       <c r="S86" t="n">
-        <v>191</v>
+        <v>58</v>
       </c>
       <c r="T86" t="n">
-        <v>4191</v>
+        <v>4058</v>
       </c>
       <c r="U86" t="n">
         <v>1</v>
@@ -7885,19 +7885,19 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>MONITORAMENTO HIDROMETEOROLOGICO</t>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DA POLÍTICA ESTADUAL DE RECURSOS HÍDRICOS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>15000000</v>
+        <v>12250000</v>
       </c>
       <c r="AA86" t="n">
-        <v>-15000000</v>
+        <v>-12250000</v>
       </c>
     </row>
     <row r="87">
@@ -7909,18 +7909,18 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IGAM</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D87" t="n">
         <v>3</v>
       </c>
       <c r="F87" t="n">
-        <v>2241</v>
+        <v>2101</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS - IGAM</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -7930,10 +7930,10 @@
         <v>3</v>
       </c>
       <c r="J87" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K87" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L87" t="n">
         <v>80</v>
@@ -7945,19 +7945,19 @@
         <v>18</v>
       </c>
       <c r="P87" t="n">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="Q87" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="R87" t="n">
         <v>4</v>
       </c>
       <c r="S87" t="n">
-        <v>192</v>
+        <v>58</v>
       </c>
       <c r="T87" t="n">
-        <v>4192</v>
+        <v>4058</v>
       </c>
       <c r="U87" t="n">
         <v>1</v>
@@ -7967,19 +7967,19 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>SEGURANÇA DE BARRAGENS</t>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DA POLÍTICA ESTADUAL DE RECURSOS HÍDRICOS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>1100000</v>
+        <v>3500000</v>
       </c>
       <c r="AA87" t="n">
-        <v>-1100000</v>
+        <v>-3500000</v>
       </c>
     </row>
     <row r="88">
@@ -7991,18 +7991,18 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D88" t="n">
         <v>3</v>
       </c>
       <c r="F88" t="n">
-        <v>1371</v>
+        <v>2101</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -8012,10 +8012,10 @@
         <v>3</v>
       </c>
       <c r="J88" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K88" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L88" t="n">
         <v>80</v>
@@ -8027,19 +8027,19 @@
         <v>18</v>
       </c>
       <c r="P88" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Q88" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="R88" t="n">
         <v>4</v>
       </c>
       <c r="S88" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="T88" t="n">
-        <v>4038</v>
+        <v>4056</v>
       </c>
       <c r="U88" t="n">
         <v>1</v>
@@ -8049,19 +8049,19 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>FISCALIZAÇÃO AMBIENTAL</t>
+          <t>RECUPERAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>100000</v>
+        <v>440000</v>
       </c>
       <c r="AA88" t="n">
-        <v>-100000</v>
+        <v>-440000</v>
       </c>
     </row>
     <row r="89">
@@ -8073,18 +8073,18 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D89" t="n">
         <v>3</v>
       </c>
       <c r="F89" t="n">
-        <v>1371</v>
+        <v>2101</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -8094,10 +8094,10 @@
         <v>3</v>
       </c>
       <c r="J89" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K89" t="n">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="L89" t="n">
         <v>80</v>
@@ -8109,19 +8109,19 @@
         <v>18</v>
       </c>
       <c r="P89" t="n">
-        <v>122</v>
+        <v>543</v>
       </c>
       <c r="Q89" t="n">
-        <v>705</v>
+        <v>31</v>
       </c>
       <c r="R89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S89" t="n">
-        <v>500</v>
+        <v>56</v>
       </c>
       <c r="T89" t="n">
-        <v>2500</v>
+        <v>4056</v>
       </c>
       <c r="U89" t="n">
         <v>1</v>
@@ -8131,19 +8131,19 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>ASSESSORAMENTO E GERENCIAMENTO DE POLÍTICAS PÚBLICAS</t>
+          <t>RECUPERAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>12000000</v>
+        <v>19200000</v>
       </c>
       <c r="AA89" t="n">
-        <v>-12000000</v>
+        <v>-19200000</v>
       </c>
     </row>
     <row r="90">
@@ -8155,18 +8155,18 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D90" t="n">
         <v>3</v>
       </c>
       <c r="F90" t="n">
-        <v>1371</v>
+        <v>2101</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -8179,7 +8179,7 @@
         <v>90</v>
       </c>
       <c r="K90" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L90" t="n">
         <v>80</v>
@@ -8191,19 +8191,19 @@
         <v>18</v>
       </c>
       <c r="P90" t="n">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q90" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="R90" t="n">
         <v>4</v>
       </c>
       <c r="S90" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="T90" t="n">
-        <v>4038</v>
+        <v>4059</v>
       </c>
       <c r="U90" t="n">
         <v>1</v>
@@ -8213,19 +8213,19 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>FISCALIZAÇÃO AMBIENTAL</t>
+          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z90" t="n">
-        <v>900000</v>
+        <v>3700000</v>
       </c>
       <c r="AA90" t="n">
-        <v>-900000</v>
+        <v>-3700000</v>
       </c>
     </row>
     <row r="91">
@@ -8237,31 +8237,31 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>1371</v>
+        <v>2101</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>90</v>
       </c>
       <c r="K91" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L91" t="n">
         <v>80</v>
@@ -8273,19 +8273,19 @@
         <v>18</v>
       </c>
       <c r="P91" t="n">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q91" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="R91" t="n">
         <v>4</v>
       </c>
       <c r="S91" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="T91" t="n">
-        <v>4038</v>
+        <v>4500</v>
       </c>
       <c r="U91" t="n">
         <v>1</v>
@@ -8295,19 +8295,19 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>FISCALIZAÇÃO AMBIENTAL</t>
+          <t>REGULARIZAÇÃO FUNDIÁRIA DE UNIDADES DE CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>350000</v>
+        <v>1500000</v>
       </c>
       <c r="AA91" t="n">
-        <v>-350000</v>
+        <v>-1500000</v>
       </c>
     </row>
     <row r="92">
@@ -8319,31 +8319,31 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D92" t="n">
         <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>1371</v>
+        <v>2101</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
         <v>90</v>
       </c>
       <c r="K92" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L92" t="n">
         <v>80</v>
@@ -8355,19 +8355,19 @@
         <v>18</v>
       </c>
       <c r="P92" t="n">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q92" t="n">
-        <v>705</v>
+        <v>31</v>
       </c>
       <c r="R92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S92" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="T92" t="n">
-        <v>1074</v>
+        <v>4059</v>
       </c>
       <c r="U92" t="n">
         <v>1</v>
@@ -8377,19 +8377,19 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>TRANSFORMAÇÃO DIGITAL DO SISEMA</t>
+          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>6600000</v>
+        <v>1000000</v>
       </c>
       <c r="AA92" t="n">
-        <v>-6600000</v>
+        <v>-1000000</v>
       </c>
     </row>
     <row r="93">
@@ -8401,31 +8401,31 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D93" t="n">
         <v>3</v>
       </c>
       <c r="F93" t="n">
-        <v>1371</v>
+        <v>2101</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>90</v>
       </c>
       <c r="K93" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="L93" t="n">
         <v>80</v>
@@ -8437,19 +8437,19 @@
         <v>18</v>
       </c>
       <c r="P93" t="n">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q93" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="R93" t="n">
         <v>4</v>
       </c>
       <c r="S93" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="T93" t="n">
-        <v>4038</v>
+        <v>4054</v>
       </c>
       <c r="U93" t="n">
         <v>1</v>
@@ -8459,19 +8459,19 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>FISCALIZAÇÃO AMBIENTAL</t>
+          <t>PREVENÇÃO E COMBATE A INCÊNDIOS FLORESTAIS</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>1150000</v>
+        <v>990000</v>
       </c>
       <c r="AA93" t="n">
-        <v>-1150000</v>
+        <v>-990000</v>
       </c>
     </row>
     <row r="94">
@@ -8479,22 +8479,22 @@
         <v>2027</v>
       </c>
       <c r="B94" t="n">
-        <v>1480</v>
+        <v>1370</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D94" t="n">
         <v>3</v>
       </c>
       <c r="F94" t="n">
-        <v>4251</v>
+        <v>2101</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -8504,10 +8504,10 @@
         <v>3</v>
       </c>
       <c r="J94" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="K94" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L94" t="n">
         <v>80</v>
@@ -8516,22 +8516,22 @@
         <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="P94" t="n">
-        <v>244</v>
+        <v>541</v>
       </c>
       <c r="Q94" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="R94" t="n">
         <v>4</v>
       </c>
       <c r="S94" t="n">
-        <v>402</v>
+        <v>58</v>
       </c>
       <c r="T94" t="n">
-        <v>4402</v>
+        <v>4058</v>
       </c>
       <c r="U94" t="n">
         <v>1</v>
@@ -8541,19 +8541,19 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>15850920</v>
+        <v>500000</v>
       </c>
       <c r="AA94" t="n">
-        <v>-15850920</v>
+        <v>-500000</v>
       </c>
     </row>
     <row r="95">
@@ -8561,22 +8561,22 @@
         <v>2027</v>
       </c>
       <c r="B95" t="n">
-        <v>1480</v>
+        <v>1370</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D95" t="n">
         <v>3</v>
       </c>
       <c r="F95" t="n">
-        <v>4251</v>
+        <v>2101</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -8589,7 +8589,7 @@
         <v>90</v>
       </c>
       <c r="K95" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="L95" t="n">
         <v>80</v>
@@ -8598,22 +8598,22 @@
         <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="P95" t="n">
-        <v>244</v>
+        <v>541</v>
       </c>
       <c r="Q95" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="R95" t="n">
         <v>4</v>
       </c>
       <c r="S95" t="n">
-        <v>402</v>
+        <v>59</v>
       </c>
       <c r="T95" t="n">
-        <v>4402</v>
+        <v>4059</v>
       </c>
       <c r="U95" t="n">
         <v>1</v>
@@ -8623,19 +8623,19 @@
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
+          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>15082</v>
+        <v>100000</v>
       </c>
       <c r="AA95" t="n">
-        <v>-15082</v>
+        <v>-100000</v>
       </c>
     </row>
     <row r="96">
@@ -8643,22 +8643,22 @@
         <v>2027</v>
       </c>
       <c r="B96" t="n">
-        <v>1480</v>
+        <v>1370</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D96" t="n">
         <v>3</v>
       </c>
       <c r="F96" t="n">
-        <v>4251</v>
+        <v>2101</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -8671,7 +8671,7 @@
         <v>90</v>
       </c>
       <c r="K96" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L96" t="n">
         <v>80</v>
@@ -8680,22 +8680,22 @@
         <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="P96" t="n">
-        <v>244</v>
+        <v>543</v>
       </c>
       <c r="Q96" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="R96" t="n">
         <v>4</v>
       </c>
       <c r="S96" t="n">
-        <v>402</v>
+        <v>56</v>
       </c>
       <c r="T96" t="n">
-        <v>4402</v>
+        <v>4056</v>
       </c>
       <c r="U96" t="n">
         <v>1</v>
@@ -8705,19 +8705,19 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
+          <t>RECUPERAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>1479414</v>
+        <v>360000</v>
       </c>
       <c r="AA96" t="n">
-        <v>-1479414</v>
+        <v>-360000</v>
       </c>
     </row>
     <row r="97">
@@ -8725,22 +8725,22 @@
         <v>2027</v>
       </c>
       <c r="B97" t="n">
-        <v>1480</v>
+        <v>1370</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D97" t="n">
         <v>3</v>
       </c>
       <c r="F97" t="n">
-        <v>4251</v>
+        <v>2101</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -8753,7 +8753,7 @@
         <v>90</v>
       </c>
       <c r="K97" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L97" t="n">
         <v>80</v>
@@ -8762,22 +8762,22 @@
         <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="P97" t="n">
-        <v>244</v>
+        <v>541</v>
       </c>
       <c r="Q97" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="R97" t="n">
         <v>4</v>
       </c>
       <c r="S97" t="n">
-        <v>433</v>
+        <v>54</v>
       </c>
       <c r="T97" t="n">
-        <v>4433</v>
+        <v>4054</v>
       </c>
       <c r="U97" t="n">
         <v>1</v>
@@ -8787,19 +8787,19 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>GESTÃO DA POLÍTICA ESTADUAL DE ASSISTÊNCIA SOCIAL</t>
+          <t>PREVENÇÃO E COMBATE A INCÊNDIOS FLORESTAIS</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>1238033</v>
+        <v>10000</v>
       </c>
       <c r="AA97" t="n">
-        <v>-1238033</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="98">
@@ -8807,22 +8807,22 @@
         <v>2027</v>
       </c>
       <c r="B98" t="n">
-        <v>1480</v>
+        <v>1370</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D98" t="n">
         <v>3</v>
       </c>
       <c r="F98" t="n">
-        <v>4251</v>
+        <v>2101</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -8832,10 +8832,10 @@
         <v>4</v>
       </c>
       <c r="J98" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="K98" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L98" t="n">
         <v>80</v>
@@ -8844,22 +8844,22 @@
         <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="P98" t="n">
-        <v>244</v>
+        <v>541</v>
       </c>
       <c r="Q98" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="R98" t="n">
         <v>4</v>
       </c>
       <c r="S98" t="n">
-        <v>402</v>
+        <v>54</v>
       </c>
       <c r="T98" t="n">
-        <v>4402</v>
+        <v>4054</v>
       </c>
       <c r="U98" t="n">
         <v>1</v>
@@ -8869,19 +8869,19 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
+          <t>PREVENÇÃO E COMBATE A INCÊNDIOS FLORESTAIS</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>20000000</v>
+        <v>200000</v>
       </c>
       <c r="AA98" t="n">
-        <v>-20000000</v>
+        <v>-200000</v>
       </c>
     </row>
     <row r="99">
@@ -8889,35 +8889,35 @@
         <v>2027</v>
       </c>
       <c r="B99" t="n">
-        <v>1480</v>
+        <v>1370</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D99" t="n">
         <v>3</v>
       </c>
       <c r="F99" t="n">
-        <v>1481</v>
+        <v>2101</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
         <v>90</v>
       </c>
       <c r="K99" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L99" t="n">
         <v>80</v>
@@ -8926,44 +8926,44 @@
         <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="P99" t="n">
-        <v>363</v>
+        <v>541</v>
       </c>
       <c r="Q99" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="R99" t="n">
         <v>4</v>
       </c>
       <c r="S99" t="n">
-        <v>158</v>
+        <v>500</v>
       </c>
       <c r="T99" t="n">
-        <v>4158</v>
+        <v>4500</v>
       </c>
       <c r="U99" t="n">
         <v>1</v>
       </c>
       <c r="V99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>QUALIFICAÇÃO PROFISSIONAL</t>
+          <t>REGULARIZAÇÃO FUNDIÁRIA DE UNIDADES DE CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>REDE DE DESENVOLVIMENTO DA EDUCAÇÃO PROFISSIONAL</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>1890827</v>
+        <v>100000</v>
       </c>
       <c r="AA99" t="n">
-        <v>-1890827</v>
+        <v>-100000</v>
       </c>
     </row>
     <row r="100">
@@ -8971,22 +8971,22 @@
         <v>2027</v>
       </c>
       <c r="B100" t="n">
-        <v>1480</v>
+        <v>1370</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D100" t="n">
         <v>3</v>
       </c>
       <c r="F100" t="n">
-        <v>1481</v>
+        <v>2101</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -8999,7 +8999,7 @@
         <v>90</v>
       </c>
       <c r="K100" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L100" t="n">
         <v>80</v>
@@ -9008,44 +9008,44 @@
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="P100" t="n">
-        <v>363</v>
+        <v>543</v>
       </c>
       <c r="Q100" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="R100" t="n">
         <v>4</v>
       </c>
       <c r="S100" t="n">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="T100" t="n">
-        <v>4158</v>
+        <v>4056</v>
       </c>
       <c r="U100" t="n">
         <v>1</v>
       </c>
       <c r="V100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>QUALIFICAÇÃO PROFISSIONAL</t>
+          <t>RECUPERAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>REDE DE DESENVOLVIMENTO DA EDUCAÇÃO PROFISSIONAL</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z100" t="n">
-        <v>810354</v>
+        <v>1000000</v>
       </c>
       <c r="AA100" t="n">
-        <v>-810354</v>
+        <v>-1000000</v>
       </c>
     </row>
     <row r="101">
@@ -9053,35 +9053,35 @@
         <v>2027</v>
       </c>
       <c r="B101" t="n">
-        <v>1500</v>
+        <v>1370</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>3</v>
       </c>
       <c r="F101" t="n">
-        <v>1501</v>
+        <v>2101</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J101" t="n">
         <v>90</v>
       </c>
       <c r="K101" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="L101" t="n">
         <v>80</v>
@@ -9090,22 +9090,22 @@
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P101" t="n">
-        <v>122</v>
+        <v>541</v>
       </c>
       <c r="Q101" t="n">
-        <v>705</v>
+        <v>31</v>
       </c>
       <c r="R101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S101" t="n">
-        <v>417</v>
+        <v>58</v>
       </c>
       <c r="T101" t="n">
-        <v>2417</v>
+        <v>4058</v>
       </c>
       <c r="U101" t="n">
         <v>1</v>
@@ -9115,19 +9115,19 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>REMUNERAÇÃO DE PESSOAL ATIVO E ENCARGOS SOCIAIS</t>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z101" t="n">
-        <v>570000</v>
+        <v>350000</v>
       </c>
       <c r="AA101" t="n">
-        <v>-570000</v>
+        <v>-350000</v>
       </c>
     </row>
     <row r="102">
@@ -9135,59 +9135,59 @@
         <v>2027</v>
       </c>
       <c r="B102" t="n">
-        <v>1500</v>
+        <v>1370</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D102" t="n">
         <v>3</v>
       </c>
       <c r="F102" t="n">
-        <v>1501</v>
+        <v>2101</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
         <v>90</v>
       </c>
       <c r="K102" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="L102" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M102" t="n">
         <v>1</v>
       </c>
       <c r="O102" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P102" t="n">
-        <v>122</v>
+        <v>541</v>
       </c>
       <c r="Q102" t="n">
-        <v>155</v>
+        <v>31</v>
       </c>
       <c r="R102" t="n">
         <v>4</v>
       </c>
       <c r="S102" t="n">
-        <v>462</v>
+        <v>59</v>
       </c>
       <c r="T102" t="n">
-        <v>4462</v>
+        <v>4059</v>
       </c>
       <c r="U102" t="n">
         <v>1</v>
@@ -9197,19 +9197,19 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA VALE S.A EM BRUMADINHO</t>
+          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z102" t="n">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="AA102" t="n">
-        <v>-1000</v>
+        <v>-1000000</v>
       </c>
     </row>
     <row r="103">
@@ -9217,59 +9217,59 @@
         <v>2027</v>
       </c>
       <c r="B103" t="n">
-        <v>1500</v>
+        <v>1370</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D103" t="n">
         <v>3</v>
       </c>
       <c r="F103" t="n">
-        <v>1501</v>
+        <v>2101</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J103" t="n">
         <v>90</v>
       </c>
       <c r="K103" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="L103" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M103" t="n">
         <v>1</v>
       </c>
       <c r="O103" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P103" t="n">
-        <v>122</v>
+        <v>541</v>
       </c>
       <c r="Q103" t="n">
-        <v>705</v>
+        <v>31</v>
       </c>
       <c r="R103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S103" t="n">
-        <v>417</v>
+        <v>54</v>
       </c>
       <c r="T103" t="n">
-        <v>2417</v>
+        <v>4054</v>
       </c>
       <c r="U103" t="n">
         <v>1</v>
@@ -9279,19 +9279,19 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>REMUNERAÇÃO DE PESSOAL ATIVO E ENCARGOS SOCIAIS</t>
+          <t>PREVENÇÃO E COMBATE A INCÊNDIOS FLORESTAIS</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>749000</v>
+        <v>3800000</v>
       </c>
       <c r="AA103" t="n">
-        <v>-749000</v>
+        <v>-3800000</v>
       </c>
     </row>
     <row r="104">
@@ -9299,35 +9299,35 @@
         <v>2027</v>
       </c>
       <c r="B104" t="n">
-        <v>1500</v>
+        <v>1370</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D104" t="n">
         <v>3</v>
       </c>
       <c r="F104" t="n">
-        <v>1501</v>
+        <v>2101</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J104" t="n">
         <v>90</v>
       </c>
       <c r="K104" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="L104" t="n">
         <v>80</v>
@@ -9336,22 +9336,22 @@
         <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P104" t="n">
-        <v>122</v>
+        <v>541</v>
       </c>
       <c r="Q104" t="n">
-        <v>155</v>
+        <v>31</v>
       </c>
       <c r="R104" t="n">
         <v>4</v>
       </c>
       <c r="S104" t="n">
-        <v>461</v>
+        <v>58</v>
       </c>
       <c r="T104" t="n">
-        <v>4461</v>
+        <v>4058</v>
       </c>
       <c r="U104" t="n">
         <v>1</v>
@@ -9361,19 +9361,19 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="AA104" t="n">
-        <v>-120000</v>
+        <v>-150000</v>
       </c>
     </row>
     <row r="105">
@@ -9381,35 +9381,35 @@
         <v>2027</v>
       </c>
       <c r="B105" t="n">
-        <v>1500</v>
+        <v>1370</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D105" t="n">
         <v>3</v>
       </c>
       <c r="F105" t="n">
-        <v>1501</v>
+        <v>2101</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J105" t="n">
         <v>90</v>
       </c>
       <c r="K105" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="L105" t="n">
         <v>80</v>
@@ -9418,22 +9418,22 @@
         <v>1</v>
       </c>
       <c r="O105" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P105" t="n">
-        <v>122</v>
+        <v>541</v>
       </c>
       <c r="Q105" t="n">
-        <v>155</v>
+        <v>31</v>
       </c>
       <c r="R105" t="n">
         <v>4</v>
       </c>
       <c r="S105" t="n">
-        <v>461</v>
+        <v>500</v>
       </c>
       <c r="T105" t="n">
-        <v>4461</v>
+        <v>4500</v>
       </c>
       <c r="U105" t="n">
         <v>1</v>
@@ -9443,19 +9443,19 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+          <t>REGULARIZAÇÃO FUNDIÁRIA DE UNIDADES DE CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>110000</v>
+        <v>200000</v>
       </c>
       <c r="AA105" t="n">
-        <v>-110000</v>
+        <v>-200000</v>
       </c>
     </row>
     <row r="106">
@@ -9463,35 +9463,35 @@
         <v>2027</v>
       </c>
       <c r="B106" t="n">
-        <v>1500</v>
+        <v>1370</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D106" t="n">
         <v>3</v>
       </c>
       <c r="F106" t="n">
-        <v>1501</v>
+        <v>2101</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J106" t="n">
         <v>90</v>
       </c>
       <c r="K106" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="L106" t="n">
         <v>80</v>
@@ -9500,22 +9500,22 @@
         <v>1</v>
       </c>
       <c r="O106" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P106" t="n">
-        <v>122</v>
+        <v>543</v>
       </c>
       <c r="Q106" t="n">
-        <v>155</v>
+        <v>31</v>
       </c>
       <c r="R106" t="n">
         <v>4</v>
       </c>
       <c r="S106" t="n">
-        <v>461</v>
+        <v>56</v>
       </c>
       <c r="T106" t="n">
-        <v>4461</v>
+        <v>4056</v>
       </c>
       <c r="U106" t="n">
         <v>1</v>
@@ -9525,19 +9525,19 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+          <t>RECUPERAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>8077861</v>
+        <v>200000</v>
       </c>
       <c r="AA106" t="n">
-        <v>-8077861</v>
+        <v>-200000</v>
       </c>
     </row>
     <row r="107">
@@ -9545,35 +9545,35 @@
         <v>2027</v>
       </c>
       <c r="B107" t="n">
-        <v>1510</v>
+        <v>1370</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D107" t="n">
         <v>3</v>
       </c>
       <c r="F107" t="n">
-        <v>1511</v>
+        <v>2101</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H107" t="n">
         <v>4</v>
       </c>
       <c r="I107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J107" t="n">
         <v>90</v>
       </c>
       <c r="K107" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L107" t="n">
         <v>80</v>
@@ -9582,22 +9582,22 @@
         <v>1</v>
       </c>
       <c r="O107" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P107" t="n">
-        <v>181</v>
+        <v>541</v>
       </c>
       <c r="Q107" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S107" t="n">
-        <v>6</v>
+        <v>500</v>
       </c>
       <c r="T107" t="n">
-        <v>1006</v>
+        <v>4500</v>
       </c>
       <c r="U107" t="n">
         <v>1</v>
@@ -9607,19 +9607,19 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>ENFRENTAMENTO À VIOLÊNCIA CONTRA A MULHER</t>
+          <t>REGULARIZAÇÃO FUNDIÁRIA DE UNIDADES DE CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>INVESTIGAÇÃO</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>1000000</v>
+        <v>13000000</v>
       </c>
       <c r="AA107" t="n">
-        <v>-1000000</v>
+        <v>-13000000</v>
       </c>
     </row>
     <row r="108">
@@ -9627,80 +9627,1884 @@
         <v>2027</v>
       </c>
       <c r="B108" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IGAM</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>3</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2241</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS - IGAM</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>3</v>
+      </c>
+      <c r="I108" t="n">
+        <v>3</v>
+      </c>
+      <c r="J108" t="n">
+        <v>50</v>
+      </c>
+      <c r="K108" t="n">
+        <v>85</v>
+      </c>
+      <c r="L108" t="n">
+        <v>80</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" t="n">
+        <v>18</v>
+      </c>
+      <c r="P108" t="n">
+        <v>544</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>65</v>
+      </c>
+      <c r="R108" t="n">
+        <v>4</v>
+      </c>
+      <c r="S108" t="n">
+        <v>191</v>
+      </c>
+      <c r="T108" t="n">
+        <v>4191</v>
+      </c>
+      <c r="U108" t="n">
+        <v>1</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>MONITORAMENTO HIDROMETEOROLOGICO</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DA POLÍTICA ESTADUAL DE RECURSOS HÍDRICOS</t>
+        </is>
+      </c>
+      <c r="Z108" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>-15000000</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IGAM</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2241</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS - IGAM</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>3</v>
+      </c>
+      <c r="I109" t="n">
+        <v>3</v>
+      </c>
+      <c r="J109" t="n">
+        <v>90</v>
+      </c>
+      <c r="K109" t="n">
+        <v>40</v>
+      </c>
+      <c r="L109" t="n">
+        <v>80</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" t="n">
+        <v>18</v>
+      </c>
+      <c r="P109" t="n">
+        <v>544</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>65</v>
+      </c>
+      <c r="R109" t="n">
+        <v>4</v>
+      </c>
+      <c r="S109" t="n">
+        <v>192</v>
+      </c>
+      <c r="T109" t="n">
+        <v>4192</v>
+      </c>
+      <c r="U109" t="n">
+        <v>1</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>SEGURANÇA DE BARRAGENS</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DA POLÍTICA ESTADUAL DE RECURSOS HÍDRICOS</t>
+        </is>
+      </c>
+      <c r="Z109" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>-1100000</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B110" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>3</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1371</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>3</v>
+      </c>
+      <c r="I110" t="n">
+        <v>3</v>
+      </c>
+      <c r="J110" t="n">
+        <v>90</v>
+      </c>
+      <c r="K110" t="n">
+        <v>30</v>
+      </c>
+      <c r="L110" t="n">
+        <v>80</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" t="n">
+        <v>18</v>
+      </c>
+      <c r="P110" t="n">
+        <v>542</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>25</v>
+      </c>
+      <c r="R110" t="n">
+        <v>4</v>
+      </c>
+      <c r="S110" t="n">
+        <v>38</v>
+      </c>
+      <c r="T110" t="n">
+        <v>4038</v>
+      </c>
+      <c r="U110" t="n">
+        <v>1</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>FISCALIZAÇÃO AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="Z110" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>-100000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B111" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>3</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1371</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>3</v>
+      </c>
+      <c r="I111" t="n">
+        <v>3</v>
+      </c>
+      <c r="J111" t="n">
+        <v>90</v>
+      </c>
+      <c r="K111" t="n">
+        <v>37</v>
+      </c>
+      <c r="L111" t="n">
+        <v>80</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1</v>
+      </c>
+      <c r="O111" t="n">
+        <v>18</v>
+      </c>
+      <c r="P111" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>705</v>
+      </c>
+      <c r="R111" t="n">
+        <v>2</v>
+      </c>
+      <c r="S111" t="n">
+        <v>500</v>
+      </c>
+      <c r="T111" t="n">
+        <v>2500</v>
+      </c>
+      <c r="U111" t="n">
+        <v>1</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>ASSESSORAMENTO E GERENCIAMENTO DE POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+      <c r="Z111" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>-12000000</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B112" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1371</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>3</v>
+      </c>
+      <c r="I112" t="n">
+        <v>3</v>
+      </c>
+      <c r="J112" t="n">
+        <v>90</v>
+      </c>
+      <c r="K112" t="n">
+        <v>39</v>
+      </c>
+      <c r="L112" t="n">
+        <v>80</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1</v>
+      </c>
+      <c r="O112" t="n">
+        <v>18</v>
+      </c>
+      <c r="P112" t="n">
+        <v>542</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>25</v>
+      </c>
+      <c r="R112" t="n">
+        <v>4</v>
+      </c>
+      <c r="S112" t="n">
+        <v>38</v>
+      </c>
+      <c r="T112" t="n">
+        <v>4038</v>
+      </c>
+      <c r="U112" t="n">
+        <v>1</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>FISCALIZAÇÃO AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="Z112" t="n">
+        <v>900000</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>-900000</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B113" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>3</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1371</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>4</v>
+      </c>
+      <c r="I113" t="n">
+        <v>4</v>
+      </c>
+      <c r="J113" t="n">
+        <v>90</v>
+      </c>
+      <c r="K113" t="n">
+        <v>40</v>
+      </c>
+      <c r="L113" t="n">
+        <v>80</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" t="n">
+        <v>18</v>
+      </c>
+      <c r="P113" t="n">
+        <v>542</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>25</v>
+      </c>
+      <c r="R113" t="n">
+        <v>4</v>
+      </c>
+      <c r="S113" t="n">
+        <v>38</v>
+      </c>
+      <c r="T113" t="n">
+        <v>4038</v>
+      </c>
+      <c r="U113" t="n">
+        <v>1</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>FISCALIZAÇÃO AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="Z113" t="n">
+        <v>350000</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>-350000</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B114" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>3</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1371</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>4</v>
+      </c>
+      <c r="I114" t="n">
+        <v>4</v>
+      </c>
+      <c r="J114" t="n">
+        <v>90</v>
+      </c>
+      <c r="K114" t="n">
+        <v>40</v>
+      </c>
+      <c r="L114" t="n">
+        <v>80</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1</v>
+      </c>
+      <c r="O114" t="n">
+        <v>18</v>
+      </c>
+      <c r="P114" t="n">
+        <v>542</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>705</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1</v>
+      </c>
+      <c r="S114" t="n">
+        <v>74</v>
+      </c>
+      <c r="T114" t="n">
+        <v>1074</v>
+      </c>
+      <c r="U114" t="n">
+        <v>1</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>TRANSFORMAÇÃO DIGITAL DO SISEMA</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+      <c r="Z114" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>-6600000</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B115" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>3</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1371</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>4</v>
+      </c>
+      <c r="I115" t="n">
+        <v>4</v>
+      </c>
+      <c r="J115" t="n">
+        <v>90</v>
+      </c>
+      <c r="K115" t="n">
+        <v>52</v>
+      </c>
+      <c r="L115" t="n">
+        <v>80</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>18</v>
+      </c>
+      <c r="P115" t="n">
+        <v>542</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>25</v>
+      </c>
+      <c r="R115" t="n">
+        <v>4</v>
+      </c>
+      <c r="S115" t="n">
+        <v>38</v>
+      </c>
+      <c r="T115" t="n">
+        <v>4038</v>
+      </c>
+      <c r="U115" t="n">
+        <v>1</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>FISCALIZAÇÃO AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="Z115" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>-1150000</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B116" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>3</v>
+      </c>
+      <c r="F116" t="n">
+        <v>4251</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>3</v>
+      </c>
+      <c r="I116" t="n">
+        <v>3</v>
+      </c>
+      <c r="J116" t="n">
+        <v>41</v>
+      </c>
+      <c r="K116" t="n">
+        <v>41</v>
+      </c>
+      <c r="L116" t="n">
+        <v>80</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="n">
+        <v>8</v>
+      </c>
+      <c r="P116" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>71</v>
+      </c>
+      <c r="R116" t="n">
+        <v>4</v>
+      </c>
+      <c r="S116" t="n">
+        <v>402</v>
+      </c>
+      <c r="T116" t="n">
+        <v>4402</v>
+      </c>
+      <c r="U116" t="n">
+        <v>1</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+        </is>
+      </c>
+      <c r="Z116" t="n">
+        <v>15850920</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>-15850920</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B117" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>3</v>
+      </c>
+      <c r="F117" t="n">
+        <v>4251</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>3</v>
+      </c>
+      <c r="I117" t="n">
+        <v>3</v>
+      </c>
+      <c r="J117" t="n">
+        <v>90</v>
+      </c>
+      <c r="K117" t="n">
+        <v>14</v>
+      </c>
+      <c r="L117" t="n">
+        <v>80</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1</v>
+      </c>
+      <c r="O117" t="n">
+        <v>8</v>
+      </c>
+      <c r="P117" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>71</v>
+      </c>
+      <c r="R117" t="n">
+        <v>4</v>
+      </c>
+      <c r="S117" t="n">
+        <v>402</v>
+      </c>
+      <c r="T117" t="n">
+        <v>4402</v>
+      </c>
+      <c r="U117" t="n">
+        <v>1</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+        </is>
+      </c>
+      <c r="Z117" t="n">
+        <v>15082</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>-15082</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B118" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" t="n">
+        <v>4251</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>3</v>
+      </c>
+      <c r="I118" t="n">
+        <v>3</v>
+      </c>
+      <c r="J118" t="n">
+        <v>90</v>
+      </c>
+      <c r="K118" t="n">
+        <v>37</v>
+      </c>
+      <c r="L118" t="n">
+        <v>80</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1</v>
+      </c>
+      <c r="O118" t="n">
+        <v>8</v>
+      </c>
+      <c r="P118" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>71</v>
+      </c>
+      <c r="R118" t="n">
+        <v>4</v>
+      </c>
+      <c r="S118" t="n">
+        <v>402</v>
+      </c>
+      <c r="T118" t="n">
+        <v>4402</v>
+      </c>
+      <c r="U118" t="n">
+        <v>1</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+        </is>
+      </c>
+      <c r="Z118" t="n">
+        <v>1479414</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>-1479414</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B119" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>3</v>
+      </c>
+      <c r="F119" t="n">
+        <v>4251</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>3</v>
+      </c>
+      <c r="I119" t="n">
+        <v>3</v>
+      </c>
+      <c r="J119" t="n">
+        <v>90</v>
+      </c>
+      <c r="K119" t="n">
+        <v>37</v>
+      </c>
+      <c r="L119" t="n">
+        <v>80</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" t="n">
+        <v>8</v>
+      </c>
+      <c r="P119" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>71</v>
+      </c>
+      <c r="R119" t="n">
+        <v>4</v>
+      </c>
+      <c r="S119" t="n">
+        <v>433</v>
+      </c>
+      <c r="T119" t="n">
+        <v>4433</v>
+      </c>
+      <c r="U119" t="n">
+        <v>1</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>GESTÃO DA POLÍTICA ESTADUAL DE ASSISTÊNCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+        </is>
+      </c>
+      <c r="Z119" t="n">
+        <v>1238033</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>-1238033</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B120" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>3</v>
+      </c>
+      <c r="F120" t="n">
+        <v>4251</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>4</v>
+      </c>
+      <c r="I120" t="n">
+        <v>4</v>
+      </c>
+      <c r="J120" t="n">
+        <v>41</v>
+      </c>
+      <c r="K120" t="n">
+        <v>42</v>
+      </c>
+      <c r="L120" t="n">
+        <v>80</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1</v>
+      </c>
+      <c r="O120" t="n">
+        <v>8</v>
+      </c>
+      <c r="P120" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>71</v>
+      </c>
+      <c r="R120" t="n">
+        <v>4</v>
+      </c>
+      <c r="S120" t="n">
+        <v>402</v>
+      </c>
+      <c r="T120" t="n">
+        <v>4402</v>
+      </c>
+      <c r="U120" t="n">
+        <v>1</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+        </is>
+      </c>
+      <c r="Z120" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>-20000000</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B121" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>3</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>3</v>
+      </c>
+      <c r="I121" t="n">
+        <v>3</v>
+      </c>
+      <c r="J121" t="n">
+        <v>90</v>
+      </c>
+      <c r="K121" t="n">
+        <v>39</v>
+      </c>
+      <c r="L121" t="n">
+        <v>80</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" t="n">
+        <v>11</v>
+      </c>
+      <c r="P121" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>67</v>
+      </c>
+      <c r="R121" t="n">
+        <v>4</v>
+      </c>
+      <c r="S121" t="n">
+        <v>158</v>
+      </c>
+      <c r="T121" t="n">
+        <v>4158</v>
+      </c>
+      <c r="U121" t="n">
+        <v>1</v>
+      </c>
+      <c r="V121" t="n">
+        <v>1</v>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>QUALIFICAÇÃO PROFISSIONAL</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>REDE DE DESENVOLVIMENTO DA EDUCAÇÃO PROFISSIONAL</t>
+        </is>
+      </c>
+      <c r="Z121" t="n">
+        <v>1890827</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>-1890827</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B122" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>3</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>4</v>
+      </c>
+      <c r="I122" t="n">
+        <v>4</v>
+      </c>
+      <c r="J122" t="n">
+        <v>90</v>
+      </c>
+      <c r="K122" t="n">
+        <v>39</v>
+      </c>
+      <c r="L122" t="n">
+        <v>80</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="n">
+        <v>11</v>
+      </c>
+      <c r="P122" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>67</v>
+      </c>
+      <c r="R122" t="n">
+        <v>4</v>
+      </c>
+      <c r="S122" t="n">
+        <v>158</v>
+      </c>
+      <c r="T122" t="n">
+        <v>4158</v>
+      </c>
+      <c r="U122" t="n">
+        <v>1</v>
+      </c>
+      <c r="V122" t="n">
+        <v>1</v>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>QUALIFICAÇÃO PROFISSIONAL</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>REDE DE DESENVOLVIMENTO DA EDUCAÇÃO PROFISSIONAL</t>
+        </is>
+      </c>
+      <c r="Z122" t="n">
+        <v>810354</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>-810354</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B123" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>3</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1501</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>3</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" t="n">
+        <v>90</v>
+      </c>
+      <c r="K123" t="n">
+        <v>11</v>
+      </c>
+      <c r="L123" t="n">
+        <v>80</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="n">
+        <v>4</v>
+      </c>
+      <c r="P123" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>705</v>
+      </c>
+      <c r="R123" t="n">
+        <v>2</v>
+      </c>
+      <c r="S123" t="n">
+        <v>417</v>
+      </c>
+      <c r="T123" t="n">
+        <v>2417</v>
+      </c>
+      <c r="U123" t="n">
+        <v>1</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>REMUNERAÇÃO DE PESSOAL ATIVO E ENCARGOS SOCIAIS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+      <c r="Z123" t="n">
+        <v>570000</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>-570000</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>3</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1501</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>3</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" t="n">
+        <v>90</v>
+      </c>
+      <c r="K124" t="n">
+        <v>11</v>
+      </c>
+      <c r="L124" t="n">
+        <v>95</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="n">
+        <v>4</v>
+      </c>
+      <c r="P124" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>155</v>
+      </c>
+      <c r="R124" t="n">
+        <v>4</v>
+      </c>
+      <c r="S124" t="n">
+        <v>462</v>
+      </c>
+      <c r="T124" t="n">
+        <v>4462</v>
+      </c>
+      <c r="U124" t="n">
+        <v>1</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA VALE S.A EM BRUMADINHO</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+        </is>
+      </c>
+      <c r="Z124" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B125" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>3</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1501</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>3</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" t="n">
+        <v>90</v>
+      </c>
+      <c r="K125" t="n">
+        <v>11</v>
+      </c>
+      <c r="L125" t="n">
+        <v>95</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="n">
+        <v>4</v>
+      </c>
+      <c r="P125" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>705</v>
+      </c>
+      <c r="R125" t="n">
+        <v>2</v>
+      </c>
+      <c r="S125" t="n">
+        <v>417</v>
+      </c>
+      <c r="T125" t="n">
+        <v>2417</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>REMUNERAÇÃO DE PESSOAL ATIVO E ENCARGOS SOCIAIS</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+      <c r="Z125" t="n">
+        <v>749000</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>-749000</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>3</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1501</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>3</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3</v>
+      </c>
+      <c r="J126" t="n">
+        <v>90</v>
+      </c>
+      <c r="K126" t="n">
+        <v>14</v>
+      </c>
+      <c r="L126" t="n">
+        <v>80</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="n">
+        <v>4</v>
+      </c>
+      <c r="P126" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>155</v>
+      </c>
+      <c r="R126" t="n">
+        <v>4</v>
+      </c>
+      <c r="S126" t="n">
+        <v>461</v>
+      </c>
+      <c r="T126" t="n">
+        <v>4461</v>
+      </c>
+      <c r="U126" t="n">
+        <v>1</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+        </is>
+      </c>
+      <c r="Z126" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>-120000</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B127" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>3</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1501</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>3</v>
+      </c>
+      <c r="I127" t="n">
+        <v>3</v>
+      </c>
+      <c r="J127" t="n">
+        <v>90</v>
+      </c>
+      <c r="K127" t="n">
+        <v>33</v>
+      </c>
+      <c r="L127" t="n">
+        <v>80</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="n">
+        <v>4</v>
+      </c>
+      <c r="P127" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>155</v>
+      </c>
+      <c r="R127" t="n">
+        <v>4</v>
+      </c>
+      <c r="S127" t="n">
+        <v>461</v>
+      </c>
+      <c r="T127" t="n">
+        <v>4461</v>
+      </c>
+      <c r="U127" t="n">
+        <v>1</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0</v>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+        </is>
+      </c>
+      <c r="Z127" t="n">
+        <v>110000</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>-110000</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B128" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>3</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1501</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>3</v>
+      </c>
+      <c r="I128" t="n">
+        <v>3</v>
+      </c>
+      <c r="J128" t="n">
+        <v>90</v>
+      </c>
+      <c r="K128" t="n">
+        <v>37</v>
+      </c>
+      <c r="L128" t="n">
+        <v>80</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" t="n">
+        <v>4</v>
+      </c>
+      <c r="P128" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>155</v>
+      </c>
+      <c r="R128" t="n">
+        <v>4</v>
+      </c>
+      <c r="S128" t="n">
+        <v>461</v>
+      </c>
+      <c r="T128" t="n">
+        <v>4461</v>
+      </c>
+      <c r="U128" t="n">
+        <v>1</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+        </is>
+      </c>
+      <c r="Z128" t="n">
+        <v>8077861</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>-8077861</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B129" t="n">
         <v>1510</v>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
         </is>
       </c>
-      <c r="D108" t="n">
-        <v>3</v>
-      </c>
-      <c r="F108" t="n">
+      <c r="D129" t="n">
+        <v>3</v>
+      </c>
+      <c r="F129" t="n">
         <v>1511</v>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
         </is>
       </c>
-      <c r="H108" t="n">
-        <v>4</v>
-      </c>
-      <c r="I108" t="n">
-        <v>4</v>
-      </c>
-      <c r="J108" t="n">
+      <c r="H129" t="n">
+        <v>4</v>
+      </c>
+      <c r="I129" t="n">
+        <v>4</v>
+      </c>
+      <c r="J129" t="n">
         <v>90</v>
       </c>
-      <c r="K108" t="n">
+      <c r="K129" t="n">
         <v>51</v>
       </c>
-      <c r="L108" t="n">
-        <v>80</v>
-      </c>
-      <c r="M108" t="n">
-        <v>1</v>
-      </c>
-      <c r="O108" t="n">
+      <c r="L129" t="n">
+        <v>80</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="n">
         <v>6</v>
       </c>
-      <c r="P108" t="n">
+      <c r="P129" t="n">
         <v>181</v>
       </c>
-      <c r="Q108" t="n">
+      <c r="Q129" t="n">
         <v>32</v>
       </c>
-      <c r="R108" t="n">
-        <v>4</v>
-      </c>
-      <c r="S108" t="n">
+      <c r="R129" t="n">
+        <v>1</v>
+      </c>
+      <c r="S129" t="n">
+        <v>6</v>
+      </c>
+      <c r="T129" t="n">
+        <v>1006</v>
+      </c>
+      <c r="U129" t="n">
+        <v>1</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>ENFRENTAMENTO À VIOLÊNCIA CONTRA A MULHER</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>INVESTIGAÇÃO</t>
+        </is>
+      </c>
+      <c r="Z129" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>-1000000</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B130" t="n">
+        <v>1510</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>3</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1511</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>4</v>
+      </c>
+      <c r="I130" t="n">
+        <v>4</v>
+      </c>
+      <c r="J130" t="n">
+        <v>90</v>
+      </c>
+      <c r="K130" t="n">
+        <v>51</v>
+      </c>
+      <c r="L130" t="n">
+        <v>80</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" t="n">
+        <v>6</v>
+      </c>
+      <c r="P130" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>32</v>
+      </c>
+      <c r="R130" t="n">
+        <v>4</v>
+      </c>
+      <c r="S130" t="n">
         <v>63</v>
       </c>
-      <c r="T108" t="n">
+      <c r="T130" t="n">
         <v>4063</v>
       </c>
-      <c r="U108" t="n">
-        <v>1</v>
-      </c>
-      <c r="V108" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" t="inlineStr">
+      <c r="U130" t="n">
+        <v>1</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO NÚCLEO INTEGRADO DE PERÍCIAS</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>INVESTIGAÇÃO</t>
         </is>
       </c>
-      <c r="Z108" t="n">
+      <c r="Z130" t="n">
         <v>20000000</v>
       </c>
-      <c r="AA108" t="n">
+      <c r="AA130" t="n">
         <v>-20000000</v>
       </c>
     </row>

--- a/logs/logv7_divergências_bases_qdd_.xlsx
+++ b/logs/logv7_divergências_bases_qdd_.xlsx
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>30304834</v>
+        <v>30304835</v>
       </c>
       <c r="AA80" t="n">
-        <v>-30304834</v>
+        <v>-30304835</v>
       </c>
     </row>
     <row r="81">
